--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008464239976449508</v>
       </c>
       <c r="C2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>47931208</v>
+        <v>4028857</v>
       </c>
       <c r="L2" t="n">
-        <v>24872701</v>
+        <v>1568568</v>
       </c>
       <c r="M2" t="n">
-        <v>5882721</v>
+        <v>324914</v>
       </c>
       <c r="N2" t="n">
-        <v>223568</v>
+        <v>6356</v>
       </c>
       <c r="O2" t="n">
-        <v>3442116</v>
+        <v>182415</v>
       </c>
       <c r="P2" t="n">
-        <v>1301610</v>
+        <v>41898</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999097585678101</v>
+        <v>0.9999345541000366</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8301522731781006</v>
+        <v>0.710481584072113</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7069644927978516</v>
+        <v>0.5392782688140869</v>
       </c>
       <c r="T2" t="n">
-        <v>0.62327641248703</v>
+        <v>0.4005508124828339</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2014518082141876</v>
+        <v>0.04557252302765846</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6776655316352844</v>
+        <v>0.4348992109298706</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7991259694099426</v>
+        <v>0.626409113407135</v>
       </c>
       <c r="X2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>52683690</v>
+        <v>4734132</v>
       </c>
       <c r="AG2" t="n">
-        <v>32880041</v>
+        <v>3030830</v>
       </c>
       <c r="AH2" t="n">
-        <v>8825327</v>
+        <v>808192</v>
       </c>
       <c r="AI2" t="n">
-        <v>650092</v>
+        <v>59360</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5059340</v>
+        <v>461747</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558059573173523</v>
+        <v>0.9544405341148376</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118016958236694</v>
+        <v>0.9131393432617188</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582155108451843</v>
+        <v>0.8580844402313232</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6616813540458679</v>
+        <v>0.660965621471405</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020092487335205</v>
+        <v>0.902009904384613</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002029011818888065</v>
       </c>
       <c r="C3" t="n">
-        <v>3826</v>
+        <v>276</v>
       </c>
       <c r="D3" t="n">
-        <v>47931208</v>
+        <v>4028857</v>
       </c>
       <c r="E3" t="n">
-        <v>6820383</v>
+        <v>857726</v>
       </c>
       <c r="F3" t="n">
-        <v>229256</v>
+        <v>48460</v>
       </c>
       <c r="G3" t="n">
-        <v>17925</v>
+        <v>3843</v>
       </c>
       <c r="H3" t="n">
-        <v>16346</v>
+        <v>4634</v>
       </c>
       <c r="I3" t="n">
-        <v>752</v>
+        <v>160</v>
       </c>
       <c r="J3" t="n">
-        <v>110176574</v>
+        <v>10016209</v>
       </c>
       <c r="K3" t="n">
-        <v>114799261</v>
+        <v>9743901</v>
       </c>
       <c r="L3" t="n">
-        <v>133174074</v>
+        <v>11657010</v>
       </c>
       <c r="M3" t="n">
-        <v>165773630</v>
+        <v>14899590</v>
       </c>
       <c r="N3" t="n">
-        <v>177755860</v>
+        <v>16106526</v>
       </c>
       <c r="O3" t="n">
-        <v>172375410</v>
+        <v>15580070</v>
       </c>
       <c r="P3" t="n">
-        <v>177169873</v>
+        <v>16110680</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8711645603179932</v>
+        <v>0.8149055242538452</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6881969571113586</v>
+        <v>0.4706859588623047</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5713427066802979</v>
+        <v>0.344277560710907</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2273132055997849</v>
+        <v>0.07065362483263016</v>
       </c>
       <c r="V3" t="n">
-        <v>0.613247275352478</v>
+        <v>0.3559296131134033</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6115022301673889</v>
+        <v>0.2160447984933853</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>52683690</v>
+        <v>4734132</v>
       </c>
       <c r="Z3" t="n">
-        <v>2167250</v>
+        <v>194580</v>
       </c>
       <c r="AA3" t="n">
-        <v>93227</v>
+        <v>8401</v>
       </c>
       <c r="AB3" t="n">
-        <v>74908</v>
+        <v>6802</v>
       </c>
       <c r="AC3" t="n">
-        <v>291</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110182842</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>122169944</v>
+        <v>11159664</v>
       </c>
       <c r="AG3" t="n">
-        <v>140303288</v>
+        <v>12708783</v>
       </c>
       <c r="AH3" t="n">
-        <v>167871272</v>
+        <v>15252180</v>
       </c>
       <c r="AI3" t="n">
-        <v>178309683</v>
+        <v>16209192</v>
       </c>
       <c r="AJ3" t="n">
-        <v>173463040</v>
+        <v>15766935</v>
       </c>
       <c r="AK3" t="n">
-        <v>177351199</v>
+        <v>16122390</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957542359828949</v>
+        <v>0.9575594663619995</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097501635551453</v>
+        <v>0.9094722867012024</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.857134997844696</v>
+        <v>0.8563569188117981</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609823703765869</v>
+        <v>0.6598488092422485</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013718962669373</v>
+        <v>0.9009644985198975</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03200610849614379</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>9011012</v>
+        <v>1461333</v>
       </c>
       <c r="E4" t="n">
-        <v>24872701</v>
+        <v>1568568</v>
       </c>
       <c r="F4" t="n">
-        <v>1914707</v>
+        <v>239416</v>
       </c>
       <c r="G4" t="n">
-        <v>118713</v>
+        <v>22390</v>
       </c>
       <c r="H4" t="n">
-        <v>207627</v>
+        <v>38424</v>
       </c>
       <c r="I4" t="n">
-        <v>17064</v>
+        <v>2384</v>
       </c>
       <c r="J4" t="n">
-        <v>6268</v>
+        <v>413</v>
       </c>
       <c r="K4" t="n">
-        <v>9806643</v>
+        <v>1641743</v>
       </c>
       <c r="L4" t="n">
-        <v>10309691</v>
+        <v>1340075</v>
       </c>
       <c r="M4" t="n">
-        <v>3555661</v>
+        <v>486254</v>
       </c>
       <c r="N4" t="n">
-        <v>886216</v>
+        <v>133114</v>
       </c>
       <c r="O4" t="n">
-        <v>1637257</v>
+        <v>237027</v>
       </c>
       <c r="P4" t="n">
-        <v>327182</v>
+        <v>24988</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999954879283905</v>
+        <v>0.9999672770500183</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8501641154289246</v>
+        <v>0.7591193318367004</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6974545121192932</v>
+        <v>0.5026528835296631</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5961806774139404</v>
+        <v>0.3702884018421173</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2136025875806808</v>
+        <v>0.05540687218308449</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6438491344451904</v>
+        <v>0.3914715647697449</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6928364634513855</v>
+        <v>0.3212815225124359</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2275167</v>
+        <v>211204</v>
       </c>
       <c r="Z4" t="n">
-        <v>32880041</v>
+        <v>3030830</v>
       </c>
       <c r="AA4" t="n">
-        <v>912484</v>
+        <v>83661</v>
       </c>
       <c r="AB4" t="n">
-        <v>60883</v>
+        <v>5621</v>
       </c>
       <c r="AC4" t="n">
-        <v>12512</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2435960</v>
+        <v>225980</v>
       </c>
       <c r="AG4" t="n">
-        <v>3180477</v>
+        <v>288302</v>
       </c>
       <c r="AH4" t="n">
-        <v>1458019</v>
+        <v>133664</v>
       </c>
       <c r="AI4" t="n">
-        <v>332393</v>
+        <v>30448</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549627</v>
+        <v>50162</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566733241081238</v>
+        <v>0.9559974670410156</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910774827003479</v>
+        <v>0.9113021492958069</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576748967170715</v>
+        <v>0.8572198748588562</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613316535949707</v>
+        <v>0.660406768321991</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016904234886169</v>
+        <v>0.9014868140220642</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1766</v>
+        <v>126</v>
       </c>
       <c r="D5" t="n">
-        <v>567595</v>
+        <v>133160</v>
       </c>
       <c r="E5" t="n">
-        <v>2820923</v>
+        <v>358677</v>
       </c>
       <c r="F5" t="n">
-        <v>5882721</v>
+        <v>324914</v>
       </c>
       <c r="G5" t="n">
-        <v>283139</v>
+        <v>37173</v>
       </c>
       <c r="H5" t="n">
-        <v>671909</v>
+        <v>81744</v>
       </c>
       <c r="I5" t="n">
-        <v>68256</v>
+        <v>7962</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7088488</v>
+        <v>915099</v>
       </c>
       <c r="L5" t="n">
-        <v>11269134</v>
+        <v>1763947</v>
       </c>
       <c r="M5" t="n">
-        <v>4413588</v>
+        <v>618842</v>
       </c>
       <c r="N5" t="n">
-        <v>759956</v>
+        <v>83604</v>
       </c>
       <c r="O5" t="n">
-        <v>2170817</v>
+        <v>330088</v>
       </c>
       <c r="P5" t="n">
-        <v>826935</v>
+        <v>152034</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999651312828064</v>
+        <v>0.9999747276306152</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9059424996376038</v>
+        <v>0.8434228897094727</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8798677921295166</v>
+        <v>0.8099144101142883</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9556341171264648</v>
+        <v>0.9323256015777588</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9908355474472046</v>
+        <v>0.9867284893989563</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9787999391555786</v>
+        <v>0.9652707576751709</v>
       </c>
       <c r="W5" t="n">
-        <v>0.993574857711792</v>
+        <v>0.9891594648361206</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>88591</v>
+        <v>8137</v>
       </c>
       <c r="Z5" t="n">
-        <v>944516</v>
+        <v>87456</v>
       </c>
       <c r="AA5" t="n">
-        <v>8825327</v>
+        <v>808192</v>
       </c>
       <c r="AB5" t="n">
-        <v>109796</v>
+        <v>10038</v>
       </c>
       <c r="AC5" t="n">
-        <v>321116</v>
+        <v>29300</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2336006</v>
+        <v>209824</v>
       </c>
       <c r="AG5" t="n">
-        <v>3261794</v>
+        <v>301685</v>
       </c>
       <c r="AH5" t="n">
-        <v>1470982</v>
+        <v>135564</v>
       </c>
       <c r="AI5" t="n">
-        <v>333432</v>
+        <v>30600</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553593</v>
+        <v>50756</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973433792591095</v>
+        <v>0.9733120203018188</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641349911689758</v>
+        <v>0.963870108127594</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836938381195068</v>
+        <v>0.9835128784179688</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962932467460632</v>
+        <v>0.9962615370750427</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938582181930542</v>
+        <v>0.9938199520111084</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983722567558289</v>
+        <v>0.9983659982681274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>314</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>168347</v>
+        <v>25133</v>
       </c>
       <c r="E6" t="n">
-        <v>223033</v>
+        <v>24381</v>
       </c>
       <c r="F6" t="n">
-        <v>251357</v>
+        <v>24655</v>
       </c>
       <c r="G6" t="n">
-        <v>223568</v>
+        <v>6356</v>
       </c>
       <c r="H6" t="n">
-        <v>107006</v>
+        <v>8682</v>
       </c>
       <c r="I6" t="n">
-        <v>9899</v>
+        <v>742</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71687</v>
+        <v>6603</v>
       </c>
       <c r="Z6" t="n">
-        <v>58910</v>
+        <v>5375</v>
       </c>
       <c r="AA6" t="n">
-        <v>120587</v>
+        <v>11116</v>
       </c>
       <c r="AB6" t="n">
-        <v>650092</v>
+        <v>59360</v>
       </c>
       <c r="AC6" t="n">
-        <v>76956</v>
+        <v>7024</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>55608</v>
+        <v>20254</v>
       </c>
       <c r="E7" t="n">
-        <v>405538</v>
+        <v>88374</v>
       </c>
       <c r="F7" t="n">
-        <v>1066900</v>
+        <v>150734</v>
       </c>
       <c r="G7" t="n">
-        <v>411448</v>
+        <v>56986</v>
       </c>
       <c r="H7" t="n">
-        <v>3442116</v>
+        <v>182415</v>
       </c>
       <c r="I7" t="n">
-        <v>231211</v>
+        <v>13740</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8910</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328074</v>
+        <v>30153</v>
       </c>
       <c r="AB7" t="n">
-        <v>83879</v>
+        <v>7720</v>
       </c>
       <c r="AC7" t="n">
-        <v>5059340</v>
+        <v>461747</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4081</v>
+        <v>1863</v>
       </c>
       <c r="E8" t="n">
-        <v>39814</v>
+        <v>10917</v>
       </c>
       <c r="F8" t="n">
-        <v>93441</v>
+        <v>22989</v>
       </c>
       <c r="G8" t="n">
-        <v>54991</v>
+        <v>12722</v>
       </c>
       <c r="H8" t="n">
-        <v>634369</v>
+        <v>103543</v>
       </c>
       <c r="I8" t="n">
-        <v>1301610</v>
+        <v>41898</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
